--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>VAERS Immunizationpvac3</t>
+    <t>VAERS Immunization[pvac3]</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="475">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,10 +514,16 @@
     <t>Will generally be set to show that the immunization has been completed or not done.  This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>completed</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+  </si>
+  <si>
+    <t>2026: fixed value = #completed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,6 +557,9 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
+    <t>2027: target not supported</t>
+  </si>
+  <si>
     <t>Event.statusReason</t>
   </si>
   <si>
@@ -601,7 +610,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSPatient)
 </t>
   </si>
   <si>
@@ -609,6 +618,9 @@
   </si>
   <si>
     <t>The patient who either received or did not receive the immunization.</t>
+  </si>
+  <si>
+    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -728,6 +740,9 @@
   </si>
   <si>
     <t>Reflects the “reliability” of the content.</t>
+  </si>
+  <si>
+    <t>2028: fixed value = false</t>
   </si>
   <si>
     <t>RXA-9</t>
@@ -1800,7 +1815,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="58.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3241,7 +3256,7 @@
         <v>80</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>80</v>
@@ -3256,11 +3271,11 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3293,22 +3308,22 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3316,10 +3331,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3342,16 +3357,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3377,11 +3392,11 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3399,7 +3414,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3414,19 +3429,19 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3437,10 +3452,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3463,13 +3478,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3496,11 +3511,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3518,7 +3533,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3527,43 +3542,43 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3582,13 +3597,13 @@
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3639,7 +3654,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>91</v>
@@ -3654,22 +3669,22 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>80</v>
@@ -3677,10 +3692,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3703,13 +3718,13 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3760,7 +3775,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3781,16 +3796,16 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>80</v>
@@ -3798,10 +3813,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3824,16 +3839,16 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3871,17 +3886,17 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -3902,30 +3917,30 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -3947,16 +3962,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4006,7 +4021,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>91</v>
@@ -4021,33 +4036,33 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4070,13 +4085,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4127,7 +4142,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4154,10 +4169,10 @@
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>80</v>
@@ -4165,10 +4180,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4191,16 +4206,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4211,7 +4226,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -4250,7 +4265,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4265,7 +4280,7 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
@@ -4274,13 +4289,13 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>80</v>
@@ -4288,10 +4303,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4314,16 +4329,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4349,31 +4364,31 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Z21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4397,13 +4412,13 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>80</v>
@@ -4411,10 +4426,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4437,13 +4452,13 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4494,7 +4509,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4515,16 +4530,16 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -4532,10 +4547,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4558,13 +4573,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4615,7 +4630,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4639,24 +4654,24 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4679,13 +4694,13 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4736,7 +4751,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4763,7 +4778,7 @@
         <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -4774,10 +4789,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4806,7 +4821,7 @@
         <v>138</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>140</v>
@@ -4847,19 +4862,19 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4886,7 +4901,7 @@
         <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -4897,10 +4912,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4923,16 +4938,16 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4982,7 +4997,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4991,7 +5006,7 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -5020,10 +5035,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5049,13 +5064,13 @@
         <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5081,13 +5096,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5105,7 +5120,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5143,10 +5158,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5172,13 +5187,13 @@
         <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5228,7 +5243,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5255,7 +5270,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5266,10 +5281,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5292,16 +5307,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5351,7 +5366,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5366,7 +5381,7 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
@@ -5389,10 +5404,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5415,13 +5430,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5472,7 +5487,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5487,7 +5502,7 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>80</v>
@@ -5496,24 +5511,24 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5536,13 +5551,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5593,7 +5608,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5617,10 +5632,10 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5631,10 +5646,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5657,13 +5672,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5690,13 +5705,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5714,7 +5729,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5729,7 +5744,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
@@ -5738,24 +5753,24 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5778,13 +5793,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5811,13 +5826,13 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5835,7 +5850,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5850,7 +5865,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5859,24 +5874,24 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5899,13 +5914,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5956,7 +5971,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5980,10 +5995,10 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5994,10 +6009,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6020,13 +6035,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6077,7 +6092,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6098,13 +6113,13 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6115,10 +6130,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6141,13 +6156,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6198,7 +6213,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6225,7 +6240,7 @@
         <v>80</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
@@ -6236,10 +6251,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6268,7 +6283,7 @@
         <v>138</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>140</v>
@@ -6321,7 +6336,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6348,7 +6363,7 @@
         <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -6359,14 +6374,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6388,10 +6403,10 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>140</v>
@@ -6446,7 +6461,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6484,10 +6499,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6510,13 +6525,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6543,13 +6558,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6567,7 +6582,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6588,13 +6603,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6605,10 +6620,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6631,16 +6646,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6690,7 +6705,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6711,16 +6726,16 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -6728,10 +6743,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6754,13 +6769,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6811,7 +6826,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6832,13 +6847,13 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6849,10 +6864,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6875,13 +6890,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6908,13 +6923,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6932,7 +6947,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6953,13 +6968,13 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -6970,10 +6985,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6996,13 +7011,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7053,7 +7068,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7074,7 +7089,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7091,10 +7106,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7117,23 +7132,23 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="R44" t="s" s="2">
         <v>80</v>
@@ -7178,7 +7193,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7202,7 +7217,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>134</v>
@@ -7216,10 +7231,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7242,13 +7257,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7275,13 +7290,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7299,7 +7314,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7337,10 +7352,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7363,13 +7378,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7420,7 +7435,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7432,7 +7447,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7458,10 +7473,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7484,13 +7499,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7541,7 +7556,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7568,7 +7583,7 @@
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7579,10 +7594,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7611,7 +7626,7 @@
         <v>138</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
@@ -7664,7 +7679,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7691,7 +7706,7 @@
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -7702,14 +7717,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7731,10 +7746,10 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -7789,7 +7804,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7827,10 +7842,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7853,13 +7868,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7910,7 +7925,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7934,7 +7949,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>134</v>
@@ -7948,10 +7963,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7977,10 +7992,10 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8031,7 +8046,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8069,10 +8084,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8095,13 +8110,13 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8152,7 +8167,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8176,7 +8191,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8190,10 +8205,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8216,13 +8231,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8273,7 +8288,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8297,7 +8312,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>134</v>
@@ -8311,10 +8326,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8337,13 +8352,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8370,13 +8385,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8394,7 +8409,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8418,7 +8433,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>134</v>
@@ -8432,10 +8447,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8458,13 +8473,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8491,13 +8506,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8515,7 +8530,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8553,10 +8568,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8579,16 +8594,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8638,7 +8653,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8662,10 +8677,10 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8676,10 +8691,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8702,13 +8717,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8759,7 +8774,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8786,7 +8801,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8797,10 +8812,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8829,7 +8844,7 @@
         <v>138</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -8882,7 +8897,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8909,7 +8924,7 @@
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8920,14 +8935,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8949,10 +8964,10 @@
         <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>140</v>
@@ -9007,7 +9022,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9045,10 +9060,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9071,13 +9086,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9128,7 +9143,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9152,10 +9167,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9166,10 +9181,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9192,13 +9207,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9249,7 +9264,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9273,10 +9288,10 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9287,10 +9302,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9313,13 +9328,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9370,7 +9385,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9394,10 +9409,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9408,10 +9423,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9434,13 +9449,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9491,7 +9506,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9529,10 +9544,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9555,13 +9570,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9612,7 +9627,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9639,7 +9654,7 @@
         <v>80</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9650,10 +9665,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9682,7 +9697,7 @@
         <v>138</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>140</v>
@@ -9735,7 +9750,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9762,7 +9777,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9773,14 +9788,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9802,10 +9817,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9860,7 +9875,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9898,10 +9913,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9924,13 +9939,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9981,7 +9996,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10019,10 +10034,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10045,13 +10060,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10102,7 +10117,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10140,10 +10155,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10166,13 +10181,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10199,13 +10214,13 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10223,7 +10238,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10261,10 +10276,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10287,16 +10302,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10334,17 +10349,17 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -10382,13 +10397,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="B71" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="C71" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>80</v>
@@ -10410,16 +10425,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10469,7 +10484,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>91</v>
@@ -10484,7 +10499,7 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>80</v>
@@ -10507,10 +10522,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10533,16 +10548,16 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10592,7 +10607,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,7 +582,7 @@
 </t>
   </si>
   <si>
-    <t>1934: source value from ADERS - 22_PVac3_TypeBrand</t>
+    <t>1934: source value based on ADERS - 22_PVac3_TypeBrand</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -617,7 +617,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference based on ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -705,7 +705,7 @@
 </t>
   </si>
   <si>
-    <t>1940: source value from ADERS - 22_PVac3_Date</t>
+    <t>1940: source value based on ADERS - 22_PVac3_Date</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -931,7 +931,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1935: source value from ADERS - 22_PVac3_Mfgr</t>
+    <t>1935: source value based on ADERS - 22_PVac3_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -943,7 +943,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1936: source value from ADERS - 22_PVac3_Lot</t>
+    <t>1936: source value based on ADERS - 22_PVac3_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -989,7 +989,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1938: source value from ADERS - 22_PVac3_Site</t>
+    <t>1938: source value based on ADERS - 22_PVac3_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1016,7 +1016,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1937: source value from ADERS - 22_PVac3_Route</t>
+    <t>1937: source value based on ADERS - 22_PVac3_Route</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1473,7 +1473,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1939: source value from ADERS - 22_PVac3_DoseInSeries</t>
+    <t>1939: source value based on ADERS - 22_PVac3_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,7 +582,7 @@
 </t>
   </si>
   <si>
-    <t>1934: source value based on ADERS - 22_PVac3_TypeBrand</t>
+    <t>1934: source value based on ADERS - 22_PVac3_TypeBrand (22-3.1)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -617,7 +617,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference based on ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference based on ADERS - 0_Pt_ICN_Full (0)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -705,7 +705,7 @@
 </t>
   </si>
   <si>
-    <t>1940: source value based on ADERS - 22_PVac3_Date</t>
+    <t>1940: source value based on ADERS - 22_PVac3_Date (22-3.7)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -931,7 +931,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1935: source value based on ADERS - 22_PVac3_Mfgr</t>
+    <t>1935: source value based on ADERS - 22_PVac3_Mfgr (22-3.2)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -943,7 +943,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1936: source value based on ADERS - 22_PVac3_Lot</t>
+    <t>1936: source value based on ADERS - 22_PVac3_Lot (22-3.3)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -989,7 +989,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1938: source value based on ADERS - 22_PVac3_Site</t>
+    <t>1938: source value based on ADERS - 22_PVac3_Site (22-3.5)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1016,7 +1016,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1937: source value based on ADERS - 22_PVac3_Route</t>
+    <t>1937: source value based on ADERS - 22_PVac3_Route (22-3.4)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1473,7 +1473,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1939: source value based on ADERS - 22_PVac3_DoseInSeries</t>
+    <t>1939: source value based on ADERS - 22_PVac3_DoseInSeries (22-3.6)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac3.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
